--- a/data/vehicles.xlsx
+++ b/data/vehicles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\창주\Documents\GitHub\ETNERS-AI-System\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225C1EF1-E3BE-4CBF-848D-37A54E83C9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28D5DB9-36C2-42DC-B35E-2CAF86132C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="158">
   <si>
     <t>No.</t>
   </si>
@@ -61,9 +61,6 @@
     <t>대표이사</t>
   </si>
   <si>
-    <t>김경아</t>
-  </si>
-  <si>
     <t>사장/대표이사</t>
   </si>
   <si>
@@ -79,18 +76,12 @@
     <t>개발1본부</t>
   </si>
   <si>
-    <t>홍성원</t>
-  </si>
-  <si>
     <t>부사장/본부장</t>
   </si>
   <si>
     <t>128고4088</t>
   </si>
   <si>
-    <t>임영혁</t>
-  </si>
-  <si>
     <t>고문</t>
   </si>
   <si>
@@ -103,9 +94,6 @@
     <t>Enable팀</t>
   </si>
   <si>
-    <t>김윤철</t>
-  </si>
-  <si>
     <t>상무/팀장</t>
   </si>
   <si>
@@ -118,9 +106,6 @@
     <t>기술개발그룹</t>
   </si>
   <si>
-    <t>황재웅</t>
-  </si>
-  <si>
     <t>상무/그룹장</t>
   </si>
   <si>
@@ -133,9 +118,6 @@
     <t>TM팀</t>
   </si>
   <si>
-    <t>신동훈</t>
-  </si>
-  <si>
     <t>부사장</t>
   </si>
   <si>
@@ -145,27 +127,18 @@
     <t>품질안전팀</t>
   </si>
   <si>
-    <t>박형기</t>
-  </si>
-  <si>
     <t>284우6937</t>
   </si>
   <si>
     <t>MSAT팀</t>
   </si>
   <si>
-    <t>신지은</t>
-  </si>
-  <si>
     <t>253부2017</t>
   </si>
   <si>
     <t>QE팀</t>
   </si>
   <si>
-    <t>백상현</t>
-  </si>
-  <si>
     <t>부사장/팀장</t>
   </si>
   <si>
@@ -175,27 +148,18 @@
     <t>DP팀</t>
   </si>
   <si>
-    <t>장성근</t>
-  </si>
-  <si>
     <t>239머5843</t>
   </si>
   <si>
     <t>PE팀</t>
   </si>
   <si>
-    <t>홍일선</t>
-  </si>
-  <si>
     <t>383거8850</t>
   </si>
   <si>
     <t>Biometrics그룹</t>
   </si>
   <si>
-    <t>백인영</t>
-  </si>
-  <si>
     <t>113수5040</t>
   </si>
   <si>
@@ -205,45 +169,30 @@
     <t>RA팀</t>
   </si>
   <si>
-    <t>정병인</t>
-  </si>
-  <si>
     <t>260수5083</t>
   </si>
   <si>
     <t>생산운영팀</t>
   </si>
   <si>
-    <t>이상민</t>
-  </si>
-  <si>
     <t>305머8812</t>
   </si>
   <si>
     <t>인사팀</t>
   </si>
   <si>
-    <t>강대성</t>
-  </si>
-  <si>
     <t>257더6796</t>
   </si>
   <si>
     <t>Commercial본부</t>
   </si>
   <si>
-    <t>린다최</t>
-  </si>
-  <si>
     <t>208마1016</t>
   </si>
   <si>
     <t>경영지원실</t>
   </si>
   <si>
-    <t>김형준</t>
-  </si>
-  <si>
     <t>부사장/실장</t>
   </si>
   <si>
@@ -253,18 +202,12 @@
     <t>재경팀</t>
   </si>
   <si>
-    <t>이기현</t>
-  </si>
-  <si>
     <t>113수5002</t>
   </si>
   <si>
     <t>PM팀</t>
   </si>
   <si>
-    <t>정진한</t>
-  </si>
-  <si>
     <t>399무1323</t>
   </si>
   <si>
@@ -274,54 +217,36 @@
     <t>사업기획실</t>
   </si>
   <si>
-    <t>고유상</t>
-  </si>
-  <si>
     <t>399무1322</t>
   </si>
   <si>
     <t>법무팀</t>
   </si>
   <si>
-    <t>문형우</t>
-  </si>
-  <si>
     <t>157러7751</t>
   </si>
   <si>
     <t>ESG사무국</t>
   </si>
   <si>
-    <t>양철보</t>
-  </si>
-  <si>
     <t>399무1327</t>
   </si>
   <si>
     <t>PD팀</t>
   </si>
   <si>
-    <t>봉기태</t>
-  </si>
-  <si>
     <t>276무8602</t>
   </si>
   <si>
     <t>Medical팀</t>
   </si>
   <si>
-    <t>길지훈</t>
-  </si>
-  <si>
     <t>219라3058</t>
   </si>
   <si>
     <t>넥스랩</t>
   </si>
   <si>
-    <t>박재현</t>
-  </si>
-  <si>
     <t>상무</t>
   </si>
   <si>
@@ -331,9 +256,6 @@
     <t>7/3 신규차량 입고, 렌터카 반납(7/6) / 관제기기 설치(7/3)</t>
   </si>
   <si>
-    <t>육근성</t>
-  </si>
-  <si>
     <t>133무2300</t>
   </si>
   <si>
@@ -349,18 +271,12 @@
     <t>탐색팀</t>
   </si>
   <si>
-    <t>서민정</t>
-  </si>
-  <si>
     <t>172주2647</t>
   </si>
   <si>
     <t>AI팀</t>
   </si>
   <si>
-    <t>강동완</t>
-  </si>
-  <si>
     <t>172주2646</t>
   </si>
   <si>
@@ -370,15 +286,9 @@
     <t>Clinical Planning팀</t>
   </si>
   <si>
-    <t>임경수</t>
-  </si>
-  <si>
     <t>172주2648</t>
   </si>
   <si>
-    <t>채주엽</t>
-  </si>
-  <si>
     <t>k9</t>
   </si>
   <si>
@@ -388,36 +298,21 @@
     <t>SBUS(Commercial)</t>
   </si>
   <si>
-    <t>유광룡</t>
-  </si>
-  <si>
     <t>265모5590</t>
   </si>
   <si>
-    <t>이남훈</t>
-  </si>
-  <si>
     <t>265모5508</t>
   </si>
   <si>
-    <t>안소신</t>
-  </si>
-  <si>
     <t>131서2521</t>
   </si>
   <si>
     <t>RA3그룹</t>
   </si>
   <si>
-    <t>정의한</t>
-  </si>
-  <si>
     <t>131서2518</t>
   </si>
   <si>
-    <t>이경원</t>
-  </si>
-  <si>
     <t>383거8802</t>
   </si>
   <si>
@@ -427,18 +322,12 @@
     <t>법무그룹</t>
   </si>
   <si>
-    <t>손성훈</t>
-  </si>
-  <si>
     <t>282마6517</t>
   </si>
   <si>
     <t>내부회계그룹</t>
   </si>
   <si>
-    <t>조창호</t>
-  </si>
-  <si>
     <t>수석변호사/그룹장</t>
   </si>
   <si>
@@ -451,24 +340,15 @@
     <t>Compliance그룹</t>
   </si>
   <si>
-    <t>오인선</t>
-  </si>
-  <si>
     <t>239머9846</t>
   </si>
   <si>
-    <t>서소연</t>
-  </si>
-  <si>
     <t>수석변호사</t>
   </si>
   <si>
     <t>382거3962</t>
   </si>
   <si>
-    <t>윤경원</t>
-  </si>
-  <si>
     <t>182무9758</t>
   </si>
   <si>
@@ -497,6 +377,123 @@
   </si>
   <si>
     <t>358러3551</t>
+  </si>
+  <si>
+    <t>김*아</t>
+  </si>
+  <si>
+    <t>홍*원</t>
+  </si>
+  <si>
+    <t>임*혁</t>
+  </si>
+  <si>
+    <t>김*철</t>
+  </si>
+  <si>
+    <t>황*웅</t>
+  </si>
+  <si>
+    <t>신*훈</t>
+  </si>
+  <si>
+    <t>박*기</t>
+  </si>
+  <si>
+    <t>신*은</t>
+  </si>
+  <si>
+    <t>백*현</t>
+  </si>
+  <si>
+    <t>장*근</t>
+  </si>
+  <si>
+    <t>홍*선</t>
+  </si>
+  <si>
+    <t>백*영</t>
+  </si>
+  <si>
+    <t>정*인</t>
+  </si>
+  <si>
+    <t>이*민</t>
+  </si>
+  <si>
+    <t>강*성</t>
+  </si>
+  <si>
+    <t>린*최</t>
+  </si>
+  <si>
+    <t>김*준</t>
+  </si>
+  <si>
+    <t>이*현</t>
+  </si>
+  <si>
+    <t>정*한</t>
+  </si>
+  <si>
+    <t>고*상</t>
+  </si>
+  <si>
+    <t>문*우</t>
+  </si>
+  <si>
+    <t>양*보</t>
+  </si>
+  <si>
+    <t>봉*태</t>
+  </si>
+  <si>
+    <t>길*훈</t>
+  </si>
+  <si>
+    <t>박*현</t>
+  </si>
+  <si>
+    <t>육*성</t>
+  </si>
+  <si>
+    <t>서*정</t>
+  </si>
+  <si>
+    <t>강*완</t>
+  </si>
+  <si>
+    <t>임*수</t>
+  </si>
+  <si>
+    <t>채*엽</t>
+  </si>
+  <si>
+    <t>유*룡</t>
+  </si>
+  <si>
+    <t>이*훈</t>
+  </si>
+  <si>
+    <t>안*신</t>
+  </si>
+  <si>
+    <t>이*원</t>
+  </si>
+  <si>
+    <t>손*훈</t>
+  </si>
+  <si>
+    <t>조*호</t>
+  </si>
+  <si>
+    <t>오*선</t>
+  </si>
+  <si>
+    <t>서*연</t>
+  </si>
+  <si>
+    <t>윤*원</t>
   </si>
 </sst>
 </file>
@@ -990,19 +987,19 @@
         <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="J2" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
@@ -1017,25 +1014,25 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="J3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L3" s="6"/>
     </row>
@@ -1049,25 +1046,25 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="J4" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L4" s="6"/>
     </row>
@@ -1081,25 +1078,25 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="J5" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L5" s="6"/>
     </row>
@@ -1113,25 +1110,25 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L6" s="7"/>
     </row>
@@ -1145,25 +1142,25 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L7" s="6"/>
     </row>
@@ -1177,25 +1174,25 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L8" s="6"/>
     </row>
@@ -1209,25 +1206,25 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L9" s="6"/>
     </row>
@@ -1241,25 +1238,25 @@
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L10" s="6"/>
     </row>
@@ -1273,25 +1270,25 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L11" s="6"/>
     </row>
@@ -1305,25 +1302,25 @@
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L12" s="6"/>
     </row>
@@ -1337,28 +1334,28 @@
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="4" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="17.5" thickBot="1">
@@ -1371,25 +1368,25 @@
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L14" s="7"/>
     </row>
@@ -1403,25 +1400,25 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L15" s="6"/>
     </row>
@@ -1435,25 +1432,25 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="4" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L16" s="6"/>
     </row>
@@ -1467,25 +1464,25 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L17" s="6"/>
     </row>
@@ -1499,25 +1496,25 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L18" s="6"/>
     </row>
@@ -1531,25 +1528,25 @@
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L19" s="6"/>
     </row>
@@ -1563,25 +1560,25 @@
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L20" s="6"/>
     </row>
@@ -1594,28 +1591,28 @@
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L21" s="6"/>
     </row>
@@ -1629,25 +1626,25 @@
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="4" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L22" s="6"/>
     </row>
@@ -1661,25 +1658,25 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L23" s="6"/>
     </row>
@@ -1693,25 +1690,25 @@
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L24" s="6"/>
     </row>
@@ -1725,25 +1722,25 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="4" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L25" s="6"/>
     </row>
@@ -1757,28 +1754,28 @@
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="10" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="17.5" thickBot="1">
@@ -1791,26 +1788,26 @@
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
       <c r="E27" s="12" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="K27" s="14"/>
       <c r="L27" s="15" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="17.5" thickBot="1">
@@ -1821,29 +1818,29 @@
         <v>9410854290203800</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L28" s="6"/>
     </row>
@@ -1855,29 +1852,29 @@
         <v>9410854290720200</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L29" s="6"/>
     </row>
@@ -1889,29 +1886,29 @@
         <v>9410854634889200</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="8" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L30" s="6"/>
     </row>
@@ -1925,25 +1922,25 @@
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J31" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L31" s="7"/>
     </row>
@@ -1957,25 +1954,25 @@
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="12" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L32" s="7"/>
     </row>
@@ -1989,25 +1986,25 @@
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="12" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L33" s="19"/>
     </row>
@@ -2021,25 +2018,25 @@
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="16" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K34" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L34" s="7"/>
     </row>
@@ -2053,25 +2050,25 @@
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="8" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K35" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L35" s="7"/>
     </row>
@@ -2085,25 +2082,25 @@
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L36" s="21"/>
     </row>
@@ -2116,28 +2113,28 @@
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G37" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="H37" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I37" s="22" t="s">
-        <v>136</v>
-      </c>
       <c r="J37" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L37" s="18"/>
     </row>
@@ -2151,28 +2148,28 @@
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L38" s="20" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="17.5" thickBot="1">
@@ -2185,25 +2182,25 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L39" s="6"/>
     </row>
@@ -2217,25 +2214,25 @@
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L40" s="6"/>
     </row>
@@ -2249,28 +2246,28 @@
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="17.5" thickBot="1">
@@ -2283,23 +2280,23 @@
       <c r="C42" s="23"/>
       <c r="D42" s="23"/>
       <c r="E42" s="4" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="H42" s="24"/>
       <c r="I42" s="5" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L42" s="6"/>
     </row>
@@ -2313,23 +2310,23 @@
       <c r="C43" s="23"/>
       <c r="D43" s="23"/>
       <c r="E43" s="4" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="H43" s="25"/>
       <c r="I43" s="5" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L43" s="6"/>
     </row>
@@ -2343,25 +2340,25 @@
       <c r="C44" s="23"/>
       <c r="D44" s="23"/>
       <c r="E44" s="4" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L44" s="6"/>
     </row>

--- a/data/vehicles.xlsx
+++ b/data/vehicles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\창주\Documents\GitHub\ETNERS-AI-System\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28D5DB9-36C2-42DC-B35E-2CAF86132C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F4F644-A490-4A7F-B64F-FBED866C9ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="201">
   <si>
     <t>No.</t>
   </si>
@@ -494,12 +494,144 @@
   </si>
   <si>
     <t>윤*원</t>
+  </si>
+  <si>
+    <t>****854270920800</t>
+  </si>
+  <si>
+    <t>****854831224100</t>
+  </si>
+  <si>
+    <t>****854734157700</t>
+  </si>
+  <si>
+    <t>****854290718200</t>
+  </si>
+  <si>
+    <t>****854290202500</t>
+  </si>
+  <si>
+    <t>****854886984500</t>
+  </si>
+  <si>
+    <t>****854341910700</t>
+  </si>
+  <si>
+    <t>****854888926900</t>
+  </si>
+  <si>
+    <t>****854277509900</t>
+  </si>
+  <si>
+    <t>****854895415600</t>
+  </si>
+  <si>
+    <t>****854874162200</t>
+  </si>
+  <si>
+    <t>****854859103700</t>
+  </si>
+  <si>
+    <t>****854290201200</t>
+  </si>
+  <si>
+    <t>****854409959800</t>
+  </si>
+  <si>
+    <t>****854921922100</t>
+  </si>
+  <si>
+    <t>****854524468600</t>
+  </si>
+  <si>
+    <t>****854580353000</t>
+  </si>
+  <si>
+    <t>****854853578400</t>
+  </si>
+  <si>
+    <t>****854772543700</t>
+  </si>
+  <si>
+    <t>****854297605600</t>
+  </si>
+  <si>
+    <t>****854290719500</t>
+  </si>
+  <si>
+    <t>****854289800600</t>
+  </si>
+  <si>
+    <t>****854277430900</t>
+  </si>
+  <si>
+    <t>****854288198500</t>
+  </si>
+  <si>
+    <t>****854717176600</t>
+  </si>
+  <si>
+    <t>****854918378400</t>
+  </si>
+  <si>
+    <t>****854290203800</t>
+  </si>
+  <si>
+    <t>****854290720200</t>
+  </si>
+  <si>
+    <t>****854634889200</t>
+  </si>
+  <si>
+    <t>****854656310800</t>
+  </si>
+  <si>
+    <t>****854295433000</t>
+  </si>
+  <si>
+    <t>****854529038400</t>
+  </si>
+  <si>
+    <t>****854482043500</t>
+  </si>
+  <si>
+    <t>****854342847100</t>
+  </si>
+  <si>
+    <t>****854582732100</t>
+  </si>
+  <si>
+    <t>****854842677300</t>
+  </si>
+  <si>
+    <t>****854916024500</t>
+  </si>
+  <si>
+    <t>****854647240400</t>
+  </si>
+  <si>
+    <t>****854286365200</t>
+  </si>
+  <si>
+    <t>****854561253700</t>
+  </si>
+  <si>
+    <t>****854270923700</t>
+  </si>
+  <si>
+    <t>****854270922400</t>
+  </si>
+  <si>
+    <t>****854289798100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0_ "/>
+  </numFmts>
   <fonts count="8">
     <font>
       <sz val="11"/>
@@ -655,7 +787,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -731,13 +863,41 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="176" formatCode="0_ "/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -754,7 +914,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="VehicleDataTable" displayName="VehicleDataTable" ref="A1:L44">
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No."/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="하이패스/주유카드"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="하이패스/주유카드" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="유효기간"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="관제"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="부서명"/>
@@ -933,7 +1093,7 @@
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="40" customWidth="1"/>
+    <col min="12" max="12" width="43.4140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="16.5" thickBot="1">
@@ -978,8 +1138,8 @@
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
-        <v>9410854270920800</v>
+      <c r="B2" s="26" t="s">
+        <v>158</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -1008,8 +1168,8 @@
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
-        <v>9410854831224100</v>
+      <c r="B3" s="26" t="s">
+        <v>159</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -1040,8 +1200,8 @@
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>9410854734157700</v>
+      <c r="B4" s="26" t="s">
+        <v>160</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -1072,8 +1232,8 @@
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>9410854290718200</v>
+      <c r="B5" s="26" t="s">
+        <v>161</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -1104,8 +1264,8 @@
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
-        <v>9410854290202500</v>
+      <c r="B6" s="26" t="s">
+        <v>162</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -1136,8 +1296,8 @@
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="4">
-        <v>9410854886984500</v>
+      <c r="B7" s="26" t="s">
+        <v>163</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -1168,8 +1328,8 @@
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="5">
-        <v>9410854341910700</v>
+      <c r="B8" s="27" t="s">
+        <v>164</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1200,8 +1360,8 @@
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
-        <v>9410854888926900</v>
+      <c r="B9" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1232,8 +1392,8 @@
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
-        <v>9410854277509900</v>
+      <c r="B10" s="26" t="s">
+        <v>166</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1264,8 +1424,8 @@
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
-        <v>9410854895415600</v>
+      <c r="B11" s="26" t="s">
+        <v>167</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1296,8 +1456,8 @@
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="4">
-        <v>9410854874162200</v>
+      <c r="B12" s="26" t="s">
+        <v>168</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1328,8 +1488,8 @@
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="5">
-        <v>9410854859103700</v>
+      <c r="B13" s="27" t="s">
+        <v>169</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -1362,8 +1522,8 @@
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="4">
-        <v>9410854290201200</v>
+      <c r="B14" s="26" t="s">
+        <v>170</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1394,8 +1554,8 @@
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="4">
-        <v>9410854409959800</v>
+      <c r="B15" s="26" t="s">
+        <v>171</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1426,8 +1586,8 @@
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="8">
-        <v>9410854921922100</v>
+      <c r="B16" s="28" t="s">
+        <v>172</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -1458,8 +1618,8 @@
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="8">
-        <v>9410854524468600</v>
+      <c r="B17" s="28" t="s">
+        <v>173</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -1490,8 +1650,8 @@
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="5">
-        <v>9410854580353000</v>
+      <c r="B18" s="27" t="s">
+        <v>174</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -1522,8 +1682,8 @@
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="5">
-        <v>9410854853578400</v>
+      <c r="B19" s="27" t="s">
+        <v>175</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -1554,8 +1714,8 @@
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="5">
-        <v>9410854772543700</v>
+      <c r="B20" s="27" t="s">
+        <v>176</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -1586,8 +1746,8 @@
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="5">
-        <v>9410854297605600</v>
+      <c r="B21" s="27" t="s">
+        <v>177</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5" t="s">
@@ -1620,8 +1780,8 @@
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="5">
-        <v>9410854290719500</v>
+      <c r="B22" s="27" t="s">
+        <v>178</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -1652,8 +1812,8 @@
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="4">
-        <v>9410854289800600</v>
+      <c r="B23" s="26" t="s">
+        <v>179</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1684,8 +1844,8 @@
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="4">
-        <v>9410854277430900</v>
+      <c r="B24" s="26" t="s">
+        <v>180</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1716,8 +1876,8 @@
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="8">
-        <v>9410854288198500</v>
+      <c r="B25" s="28" t="s">
+        <v>181</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -1748,8 +1908,8 @@
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="9">
-        <v>9410854717176600</v>
+      <c r="B26" s="29" t="s">
+        <v>182</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -1782,8 +1942,8 @@
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="12">
-        <v>9410854918378400</v>
+      <c r="B27" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -1814,8 +1974,8 @@
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="16">
-        <v>9410854290203800</v>
+      <c r="B28" s="31" t="s">
+        <v>184</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>81</v>
@@ -1848,8 +2008,8 @@
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="8">
-        <v>9410854290720200</v>
+      <c r="B29" s="28" t="s">
+        <v>185</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>81</v>
@@ -1882,8 +2042,8 @@
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="8">
-        <v>9410854634889200</v>
+      <c r="B30" s="28" t="s">
+        <v>186</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>86</v>
@@ -1916,8 +2076,8 @@
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="9">
-        <v>9410854656310800</v>
+      <c r="B31" s="29" t="s">
+        <v>187</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -1948,8 +2108,8 @@
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="12">
-        <v>9410854295433000</v>
+      <c r="B32" s="30" t="s">
+        <v>188</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -1980,8 +2140,8 @@
       <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="12">
-        <v>9410854529038400</v>
+      <c r="B33" s="30" t="s">
+        <v>189</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -2012,8 +2172,8 @@
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="12">
-        <v>9410854482043500</v>
+      <c r="B34" s="30" t="s">
+        <v>190</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
@@ -2044,8 +2204,8 @@
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="16">
-        <v>9410854342847100</v>
+      <c r="B35" s="31" t="s">
+        <v>191</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
@@ -2076,8 +2236,8 @@
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="9">
-        <v>9410854582732100</v>
+      <c r="B36" s="29" t="s">
+        <v>192</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -2108,8 +2268,8 @@
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="17">
-        <v>9410854842677300</v>
+      <c r="B37" s="32" t="s">
+        <v>193</v>
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17" t="s">
@@ -2142,8 +2302,8 @@
       <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" s="4">
-        <v>9410854916024500</v>
+      <c r="B38" s="26" t="s">
+        <v>194</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -2176,8 +2336,8 @@
       <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" s="4">
-        <v>9410854647240400</v>
+      <c r="B39" s="26" t="s">
+        <v>195</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -2208,8 +2368,8 @@
       <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="4">
-        <v>9410854286365200</v>
+      <c r="B40" s="26" t="s">
+        <v>196</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -2240,8 +2400,8 @@
       <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" s="4">
-        <v>9410854561253700</v>
+      <c r="B41" s="26" t="s">
+        <v>197</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -2274,8 +2434,8 @@
       <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="23">
-        <v>9410854270923700</v>
+      <c r="B42" s="33" t="s">
+        <v>198</v>
       </c>
       <c r="C42" s="23"/>
       <c r="D42" s="23"/>
@@ -2304,8 +2464,8 @@
       <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="23">
-        <v>9410854270922400</v>
+      <c r="B43" s="33" t="s">
+        <v>199</v>
       </c>
       <c r="C43" s="23"/>
       <c r="D43" s="23"/>
@@ -2334,8 +2494,8 @@
       <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="23">
-        <v>9410854289798100</v>
+      <c r="B44" s="33" t="s">
+        <v>200</v>
       </c>
       <c r="C44" s="23"/>
       <c r="D44" s="23"/>
